--- a/static/data/exports/Retro_PB_AE_2017.xlsx
+++ b/static/data/exports/Retro_PB_AE_2017.xlsx
@@ -6374,11 +6374,11 @@
       </c>
       <c r="C81" t="inlineStr">
         <is>
-          <t>CPM</t>
+          <t>CPI(M)</t>
         </is>
       </c>
       <c r="D81" t="n">
-        <v>22328</v>
+        <v>22339</v>
       </c>
       <c r="E81" t="n">
         <v>356</v>
@@ -18130,11 +18130,11 @@
       </c>
       <c r="C240" t="inlineStr">
         <is>
-          <t>CPM</t>
+          <t>CPI(M)</t>
         </is>
       </c>
       <c r="D240" t="n">
-        <v>22328</v>
+        <v>22339</v>
       </c>
       <c r="E240" t="n">
         <v>1115</v>
@@ -25562,11 +25562,11 @@
       </c>
       <c r="C341" t="inlineStr">
         <is>
-          <t>CPM</t>
+          <t>CPI(M)</t>
         </is>
       </c>
       <c r="D341" t="n">
-        <v>22328</v>
+        <v>22339</v>
       </c>
       <c r="E341" t="n">
         <v>903</v>
@@ -30359,11 +30359,11 @@
       </c>
       <c r="C406" t="inlineStr">
         <is>
-          <t>CPM</t>
+          <t>CPI(M)</t>
         </is>
       </c>
       <c r="D406" t="n">
-        <v>22328</v>
+        <v>22339</v>
       </c>
       <c r="E406" t="n">
         <v>791</v>
@@ -35743,11 +35743,11 @@
       </c>
       <c r="C479" t="inlineStr">
         <is>
-          <t>CPM</t>
+          <t>CPI(M)</t>
         </is>
       </c>
       <c r="D479" t="n">
-        <v>22328</v>
+        <v>22339</v>
       </c>
       <c r="E479" t="n">
         <v>2217</v>
@@ -37292,11 +37292,11 @@
       </c>
       <c r="C500" t="inlineStr">
         <is>
-          <t>CPM</t>
+          <t>CPI(M)</t>
         </is>
       </c>
       <c r="D500" t="n">
-        <v>22328</v>
+        <v>22339</v>
       </c>
       <c r="E500" t="n">
         <v>881</v>
@@ -38029,11 +38029,11 @@
       </c>
       <c r="C510" t="inlineStr">
         <is>
-          <t>CPM</t>
+          <t>CPI(M)</t>
         </is>
       </c>
       <c r="D510" t="n">
-        <v>22328</v>
+        <v>22339</v>
       </c>
       <c r="E510" t="n">
         <v>1176</v>
@@ -38916,11 +38916,11 @@
       </c>
       <c r="C522" t="inlineStr">
         <is>
-          <t>CPM</t>
+          <t>CPI(M)</t>
         </is>
       </c>
       <c r="D522" t="n">
-        <v>22328</v>
+        <v>22339</v>
       </c>
       <c r="E522" t="n">
         <v>1026</v>
@@ -54693,11 +54693,11 @@
       </c>
       <c r="C736" t="inlineStr">
         <is>
-          <t>CPM</t>
+          <t>CPI(M)</t>
         </is>
       </c>
       <c r="D736" t="n">
-        <v>22328</v>
+        <v>22339</v>
       </c>
       <c r="E736" t="n">
         <v>662</v>
@@ -55355,11 +55355,11 @@
       </c>
       <c r="C745" t="inlineStr">
         <is>
-          <t>CPM</t>
+          <t>CPI(M)</t>
         </is>
       </c>
       <c r="D745" t="n">
-        <v>22328</v>
+        <v>22339</v>
       </c>
       <c r="E745" t="n">
         <v>546</v>
@@ -80227,11 +80227,11 @@
       </c>
       <c r="C1082" t="inlineStr">
         <is>
-          <t>CPM</t>
+          <t>CPI(M)</t>
         </is>
       </c>
       <c r="D1082" t="n">
-        <v>22328</v>
+        <v>22339</v>
       </c>
       <c r="E1082" t="n">
         <v>911</v>
@@ -81414,11 +81414,11 @@
       </c>
       <c r="C1098" t="inlineStr">
         <is>
-          <t>CPIM</t>
+          <t>CPI(M)</t>
         </is>
       </c>
       <c r="D1098" t="n">
-        <v>22461</v>
+        <v>22339</v>
       </c>
       <c r="E1098" t="n">
         <v>376</v>
@@ -84428,26 +84428,26 @@
     </row>
     <row r="1139">
       <c r="A1139" t="n">
-        <v>1743293</v>
+        <v>1743292</v>
       </c>
       <c r="B1139" t="inlineStr">
         <is>
-          <t>Karnail Singh</t>
+          <t>Gurdarshan Singh</t>
         </is>
       </c>
       <c r="C1139" t="inlineStr">
         <is>
-          <t>SAD(A)</t>
+          <t>DEMSWP</t>
         </is>
       </c>
       <c r="D1139" t="n">
-        <v>22321</v>
+        <v>22366</v>
       </c>
       <c r="E1139" t="n">
         <v>600</v>
       </c>
       <c r="F1139" t="n">
-        <v>0.46</v>
+        <v>0.456089940936352</v>
       </c>
       <c r="G1139" t="n">
         <v>7</v>
@@ -84465,12 +84465,12 @@
       </c>
       <c r="K1139" t="inlineStr">
         <is>
-          <t>Karnail Singh</t>
+          <t>Gurdarshan Singh</t>
         </is>
       </c>
       <c r="L1139" t="inlineStr">
         <is>
-          <t>SAD(A)</t>
+          <t>DEMSWP</t>
         </is>
       </c>
       <c r="N1139" t="inlineStr">
@@ -84484,7 +84484,7 @@
         </is>
       </c>
       <c r="P1139" t="n">
-        <v>70</v>
+        <v>49</v>
       </c>
       <c r="Q1139" t="b">
         <v>0</v>
@@ -84503,26 +84503,26 @@
     </row>
     <row r="1140">
       <c r="A1140" t="n">
-        <v>1743292</v>
+        <v>1743293</v>
       </c>
       <c r="B1140" t="inlineStr">
         <is>
-          <t>Gurdarshan Singh</t>
+          <t>Karnail Singh</t>
         </is>
       </c>
       <c r="C1140" t="inlineStr">
         <is>
-          <t>DEMSWP</t>
+          <t>SAD(A)</t>
         </is>
       </c>
       <c r="D1140" t="n">
-        <v>22366</v>
+        <v>22321</v>
       </c>
       <c r="E1140" t="n">
         <v>600</v>
       </c>
       <c r="F1140" t="n">
-        <v>0.456089940936352</v>
+        <v>0.46</v>
       </c>
       <c r="G1140" t="n">
         <v>7</v>
@@ -84540,12 +84540,12 @@
       </c>
       <c r="K1140" t="inlineStr">
         <is>
-          <t>Gurdarshan Singh</t>
+          <t>Karnail Singh</t>
         </is>
       </c>
       <c r="L1140" t="inlineStr">
         <is>
-          <t>DEMSWP</t>
+          <t>SAD(A)</t>
         </is>
       </c>
       <c r="N1140" t="inlineStr">
@@ -84559,7 +84559,7 @@
         </is>
       </c>
       <c r="P1140" t="n">
-        <v>49</v>
+        <v>70</v>
       </c>
       <c r="Q1140" t="b">
         <v>0</v>
@@ -91083,11 +91083,11 @@
       </c>
       <c r="C1229" t="inlineStr">
         <is>
-          <t>CPM</t>
+          <t>CPI(M)</t>
         </is>
       </c>
       <c r="D1229" t="n">
-        <v>22328</v>
+        <v>22339</v>
       </c>
       <c r="E1229" t="n">
         <v>317</v>
